--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 3 INDICADORES/3 indicadores.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 3 INDICADORES/3 indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 3 INDICADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB3CD11-921B-43C7-8996-35471B7E2616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCC8CFD-C230-4946-891E-9A72B3B42AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
@@ -92,22 +92,22 @@
     <t>campoq</t>
   </si>
   <si>
-    <t>13.04.2026</t>
-  </si>
-  <si>
     <t>I TRIMESTRE</t>
   </si>
   <si>
-    <t>SPORT MEDICAL CENTER IPS GUSTAVO PORTELA S.A.S.</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DIAGNÓSTICO MEDICO SA - IDIME SA</t>
-  </si>
-  <si>
-    <t>0344-2022</t>
-  </si>
-  <si>
-    <t>0700-2024</t>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>0380-2025</t>
+  </si>
+  <si>
+    <t>0380-2026</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL LOCAL</t>
+  </si>
+  <si>
+    <t>CLINICA COLSANITAS SA</t>
   </si>
 </sst>
 </file>
@@ -552,37 +552,38 @@
     </row>
     <row r="2" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H2" s="1">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I2" s="1">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="J2" s="1">
-        <v>284</v>
+        <f>I2/2</f>
+        <v>42</v>
       </c>
       <c r="K2" s="1">
-        <v>284</v>
+        <v>42</v>
       </c>
       <c r="L2" s="2" t="str">
         <f t="shared" ref="L2:L3" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
@@ -611,16 +612,16 @@
     </row>
     <row r="3" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -629,19 +630,21 @@
         <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1">
-        <v>4</v>
+        <f>AVERAGE(E3:G3)</f>
+        <v>5</v>
       </c>
       <c r="I3" s="1">
-        <v>4349</v>
+        <v>106</v>
       </c>
       <c r="J3" s="1">
-        <v>2174</v>
+        <f>I3/2</f>
+        <v>53</v>
       </c>
       <c r="K3" s="1">
-        <v>2174</v>
+        <v>53</v>
       </c>
       <c r="L3" s="2" t="str">
         <f t="shared" si="0"/>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 3 INDICADORES/3 indicadores.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 3 INDICADORES/3 indicadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 3 INDICADORES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 3 INDICADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCC8CFD-C230-4946-891E-9A72B3B42AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3D091F-510D-4BD2-97BD-B840C9E2C0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>campoa</t>
   </si>
@@ -98,23 +99,17 @@
     <t>20.04.2026</t>
   </si>
   <si>
-    <t>0380-2025</t>
-  </si>
-  <si>
-    <t>0380-2026</t>
-  </si>
-  <si>
-    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL LOCAL</t>
-  </si>
-  <si>
-    <t>CLINICA COLSANITAS SA</t>
+    <t>0773-2023</t>
+  </si>
+  <si>
+    <t>ESE HOSPITAL DEPARTAMENTAL SAN JOSE DE NEIRA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,19 +480,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="11.42578125" style="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="11.375" style="1"/>
+    <col min="12" max="12" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="85.5">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -558,116 +553,54 @@
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H2" s="1">
-        <v>4.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1">
-        <f>I2/2</f>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K2" s="1">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2" t="str">
-        <f t="shared" ref="L2:L3" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="L2" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="M2" s="2" t="str">
-        <f t="shared" ref="M2:M3" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="M2" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="N2" s="2" t="str">
-        <f t="shared" ref="N2:N3" si="2">IF(G2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="N2" si="2">IF(G2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="O2" s="2" t="str">
-        <f t="shared" ref="O2:O3" si="3">IF(H2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
+        <f t="shared" ref="O2" si="3">IF(H2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
         <v>Cumplimiento en la evaluación de los indicadores.</v>
       </c>
       <c r="P2" s="2" t="str">
-        <f t="shared" ref="P2:P3" si="4">IF(H2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
+        <f t="shared" ref="P2" si="4">IF(H2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
         <v>No se requiere plan de mejora.</v>
       </c>
       <c r="Q2" s="2" t="str">
-        <f t="shared" ref="Q2:Q3" si="5">IF(H2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1">
-        <f>AVERAGE(E3:G3)</f>
-        <v>5</v>
-      </c>
-      <c r="I3" s="1">
-        <v>106</v>
-      </c>
-      <c r="J3" s="1">
-        <f>I3/2</f>
-        <v>53</v>
-      </c>
-      <c r="K3" s="1">
-        <v>53</v>
-      </c>
-      <c r="L3" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M3" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="N3" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="Q2" si="5">IF(H2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
         <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
       </c>
     </row>
